--- a/xe_mau.xlsx
+++ b/xe_mau.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="DANH SACH XE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="HƯỚNG DẪN" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,51 +26,47 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="006366F1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="0064748B"/>
+      <name val="Segoe UI"/>
+      <color rgb="00713F12"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00374151"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
       <b val="1"/>
+      <color rgb="004338CA"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Segoe UI"/>
+      <color rgb="001E293B"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="006366F1"/>
-      <sz val="10"/>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -80,17 +75,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF2FF"/>
+        <fgColor rgb="001E1B4B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF7ED"/>
+        <fgColor rgb="00FEF9C3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E293B"/>
+        <fgColor rgb="006366F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF2FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -108,8 +108,13 @@
         <fgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -119,37 +124,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00C7D2FE"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00C7D2FE"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="006366F1"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CBD5E1"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CBD5E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00C7D2FE"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00C7D2FE"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -160,31 +151,32 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -551,33 +543,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="38" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏭  WMS — DANH SÁCH XE NHẬP KHO</t>
+          <t>🏭  WMS — DANH SÁCH XE NHẬP KHO (VINFAST)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Lưu ý: Các cột có dấu (*) là BẮT BUỘC. VIN phải đúng 17 ký tự, không dấu cách. Không xoá hoặc đổi tên cột tiêu đề.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
+          <t>⚠️  Lưu ý: Cột có dấu (*) là BẮT BUỘC. VIN phải đúng 17 ký tự, chữ IN HOA. Không xoá / đổi tên cột tiêu đề. PO_NUMBER và NOTE là tuỳ chọn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>VIN *</t>
@@ -614,457 +606,308 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>BẮT BUỘC — 17 ký tự, chữ IN HOA, không dấu</t>
+          <t>BẮT BUỘC — 17 ký tự, IN HOA, không dấu cách</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>BẮT BUỘC — Tên dòng xe</t>
+          <t>BẮT BUỘC — Tên dòng xe (VD: VF8, VF9...)</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>BẮT BUỘC — Màu xe</t>
+          <t>BẮT BUỘC — Màu xe (VD: Trắng Tinh Khôi)</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>BẮT BUỘC — Phiên bản / tiêu chuẩn / đặc biệt</t>
+          <t>BẮT BUỘC — Phiên bản (VD: Plus, Eco, Base)</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>BẮT BUỘC — Năm sản xuất (4 chữ số)</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Số PO đơn hàng (tuỳ chọn)</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Ghi chú thêm (tuỳ chọn)</t>
+          <t>BẮT BUỘC — 4 chữ số (VD: 2025)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Tuỳ chọn — Mã đơn hàng PO</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Tuỳ chọn — Ghi chú thêm</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>JTMRFREV8JD123456</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Toyota Fortuner</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Trắng Ngọc Trai</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>2.4G 4x2 AT</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>PO-2024-001</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>VF9JTDKG7M0123401</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>VF9</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Trắng Tinh Khôi</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Plus</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>PO-2025-001</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>VF3E29R4XME234567</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Hyundai Tucson</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Xanh Thiên Thanh</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>2.0 Premium</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>PO-2024-002</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr"/>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>VF8A28MZ4N0123402</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>VF8</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Đen Huyền Bí</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Plus</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>PO-2025-002</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>SALWA2FK5HA345678</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Mitsubishi Xpander</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Đỏ Garnet</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>1.5 MT STD</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>PO-2025-001</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>VF7C14FK5P0123403</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>VF7</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Xanh Dương Đại Dương</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Plus</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>PO-2025-003</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>VF6B16HX8N0123404</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>VF6</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Đỏ Ruby</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Plus</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>PO-2024-004</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>VF5A12GZ2M0123405</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>VF5</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Xám Bạc Hà</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>PO-2024-005</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Đặt hàng đặc biệt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>VF3E10RX6L0123406</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>VF3</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Trắng Tinh Khôi</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F10" s="10" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>VFELA18FX0N123407</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>VF e34</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Xanh Biển Nước Sâu</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>PO-2024-007</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>VFLAD10FX5M123408</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Fadil</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Bạc Ánh Kim</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>PO-2025-008</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Ưu tiên giao trước</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>WBA3A5C51EF456789</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Kia Seltos</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Đen Ánh Kim</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>1.4T Premium</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>PO-2025-002</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>1G1FH1R71H5567890</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Mazda CX-5</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Xám Titanium</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>2.5 Signature</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>PO-2024-003</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Đặt hàng đặc biệt</t>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>✅  Xoá các dòng mẫu từ dòng 5 trở xuống rồi điền dữ liệu thực. Giữ nguyên dòng 1-4 (tiêu đề, lưu ý, header, mô tả). Lưu file rồi kéo thả vào ô Import.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>📋 HƯỚNG DẪN SỬ DỤNG FILE MẪU</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="10" t="inlineStr"/>
-      <c r="B2" s="11" t="inlineStr"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>CỘT</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>MÔ TẢ CHI TIẾT</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>VIN *</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Số nhận dạng xe — đúng 17 ký tự (chữ và số). KHÔNG dùng chữ I, O, Q. Ví dụ: JTMRFREV8JD123456</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>MODEL *</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Tên dòng xe đầy đủ. Ví dụ: Toyota Fortuner, Hyundai Tucson</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>COLOR *</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Màu xe theo danh mục. Ví dụ: Trắng Ngọc Trai, Đỏ Garnet</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>VERSION *</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Phiên bản xe. Ví dụ: 2.4G 4x2 AT, 1.5 MT STD, 2.0 Premium</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>YEAR *</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>Năm sản xuất, 4 chữ số. Ví dụ: 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>PO_NUMBER</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Số đơn đặt hàng (Purchase Order). Có thể bỏ trống.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>Ghi chú nội bộ. Có thể bỏ trống.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="10" t="inlineStr"/>
-      <c r="B11" s="11" t="inlineStr"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>⚠️ LỖI THƯỜNG GẶP</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>VIN trùng</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>Hệ thống sẽ báo lỗi nếu VIN đã tồn tại trong kho</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>VIN sai độ dài</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>VIN phải đúng 17 ký tự, không được ít hơn hoặc nhiều hơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Thiếu cột bắt buộc</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>Không xoá các cột có dấu (*). Hệ thống sẽ không nhận file</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="10" t="inlineStr"/>
-      <c r="B16" s="11" t="inlineStr"/>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>📌 LƯU Ý QUAN TRỌNG</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>Định dạng file</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Chỉ hỗ trợ .xlsx và .xls (Microsoft Excel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Dòng dữ liệu</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Bắt đầu từ dòng 5 (sau header và tooltip). KHÔNG thêm dòng trắng giữa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Số lượng</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>Khuyến nghị mỗi lần import tối đa 200 xe để tránh timeout</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>Mã hoá</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>Lưu file với encoding UTF-8 để hiển thị đúng tiếng Việt có dấu</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>